--- a/EXCEL/Table.xlsx
+++ b/EXCEL/Table.xlsx
@@ -8,26 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/898af4500e89e0da/Desktop/DHRUV/Data Science and Analytics with GenAl/EXCEL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{CDC934DD-F921-4C59-B914-CD6F8D5E95BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CE794DB-60DA-4D22-A99A-10027C8CB5E7}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{CDC934DD-F921-4C59-B914-CD6F8D5E95BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF6ED0C2-1454-4151-A471-A3EEF8543F1B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{8D265CF8-5A05-4746-848A-74BBAA3872E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="Slicer_OrderID">#N/A</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
-      <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicerCache r:id="rId2"/>
-      </x15:slicerCaches>
-    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -229,105 +218,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>234315</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="8" name="OrderID">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEBBE69D-13AB-EDAD-8B4C-7A38D0022650}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="OrderID"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6301740" y="1691640"/>
-              <a:ext cx="1828800" cy="3609975"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
-                <a:t>This shape represents a table slicer. Table slicers are not supported in this version of Excel.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2007 or earlier, the slicer can't be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_OrderID" xr10:uid="{733EAAF2-522F-40BA-9D13-4BAF926BEF12}" sourceName="OrderID">
-  <extLst>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
-      <x15:tableSlicerCache tableId="1" column="1"/>
-    </x:ext>
-  </extLst>
-</slicerCacheDefinition>
-</file>
-
-<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="OrderID" xr10:uid="{95130F2C-1C9F-4760-B1AE-30B70C5DFDE3}" cache="Slicer_OrderID" caption="OrderID" rowHeight="361950"/>
-</slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -869,16 +759,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
-      <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicer r:id="rId3"/>
-      </x14:slicerList>
-    </ext>
-  </extLst>
 </worksheet>
 </file>